--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_050_Bangladesh.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_050_Bangladesh.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf4394e2039454978"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1cdf99ed0c1d4def"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rfcd24c675f3f43f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R46eda3f81d2b4e82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9287e4092981406c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R4a378b8af2424f9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rf694c431fbc04915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R09459165556b4fdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R72355c9f66704666"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R94309321b52c4c8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R193993285b234a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R109d266be2fa4c2b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ050CommercialTable" displayName="EEZ050CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ050CommercialTable" displayName="EEZ050CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ050FunctionalTable" displayName="EEZ050FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ050FunctionalTable" displayName="EEZ050FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ050ValidationTable" displayName="EEZ050ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ050ValidationTable" displayName="EEZ050ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8466,7 +8420,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1971458d521f456e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R379a923095364199"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8476,20 +8430,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8497,606 +8441,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>37522.603502586295</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2516298302384485</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>178.49655156112138</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>37522.603502586295</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>179.94043614356468</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$117,A2,'Species'!$U$2:$U$117))</x:f>
-        <x:v>6751833.639497425</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2516298302384485</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>178.49655156112138</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>6697655.330806908</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>54178.30869051721</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.008089145531469</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.008089145531469147</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>95881.4546342342</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.78009626913578</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>60.26931689835189</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>95881.4546342342</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>74.04477201066463</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$117,A3,'Species'!$U$2:$U$117))</x:f>
-        <x:v>7099520.448442754</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.78009626913578</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>60.26931689835189</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>5778709.774025611</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1320810.6744171437</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.2285649783545074</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.22856497835450734</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>7682.9327970996</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.5000486338457604</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>316.2631803133329</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>7682.9327970996</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>316.34462282851786</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$117,A4,'Species'!$U$2:$U$117))</x:f>
-        <x:v>2430454.477915323</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.5000486338457604</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>316.2631803133329</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2429828.76054433</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>625.7173709929921</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0002575150072932</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.000257515007293279</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>342617.76890162524</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.2280989641010085</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>16.908261818279314</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>342617.76890162524</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>21.82550468832337</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$117,A5,'Species'!$U$2:$U$117))</x:f>
-        <x:v>7477805.721465315</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.2280989641010085</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>16.908261818279314</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>5793070.9401833955</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1684734.7812819192</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2908189453707233</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.2908189453707232</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>25928.1030295987</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.22999960400698</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>16.982421039909386</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>25928.1030295987</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>16.982423142543826</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$117,A6,'Species'!$U$2:$U$117))</x:f>
-        <x:v>440322.0169321177</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.22999960400698</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>16.982421039909386</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>440321.9624147953</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0.05451732239453122</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0000001238124079</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>1.2381240784708898e-7</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>449921.12758548575</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.5202865940037515</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>331.34970937023894</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>449921.12758548575</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>553.2008301575094</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$117,A7,'Species'!$U$2:$U$117))</x:f>
-        <x:v>248896741.2856934</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.5202865940037515</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>331.34970937023894</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>149081234.8649809</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>99815506.4207125</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.6695376954122554</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.6695376954122554</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>148702.73694241012</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5827936590900316</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>382.64289978249417</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>148702.73694241012</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>538.3771870104862</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$117,A8,'Species'!$U$2:$U$117))</x:f>
-        <x:v>80058161.21581507</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5827936590900316</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>382.64289978249417</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>56900046.46923723</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>23158114.746577837</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.406996411841213</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.40699641184121305</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>608.7624733998999</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.631254774795343</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>427.81378550593433</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>608.7624733998999</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>439.38650431959434</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$117,A9,'Species'!$U$2:$U$117))</x:f>
-        <x:v>267482.01514813205</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.631254774795343</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>427.81378550593433</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>260436.97821916683</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>7045.036928965215</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0270508319407567</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.02705083194075678</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5583.7850035044</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.049877011115237</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1121.7007522212489</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5583.7850035044</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1121.795879049499</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$117,A10,'Species'!$U$2:$U$117))</x:f>
-        <x:v>6263867.0064296285</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.049877011115237</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1121.7007522212489</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>6263335.838672615</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>531.1677570138127</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0000848058879</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.00008480588789988671</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>133.4450531133</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.451594501725834</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2828.7495750832254</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>133.4450531133</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2896.532049417914</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$117,A11,'Species'!$U$2:$U$117))</x:f>
-        <x:v>386527.87317894923</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.451594501725834</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2828.7495750832254</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>377482.6372912058</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>9045.235887743416</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0239619918750476</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.023961991875047606</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1139a88cbc248b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d9d3b9a91e7481d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9106,20 +8656,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9127,1092 +8667,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1741.9591500860001</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.698379941509302</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>499.3211263526533</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1741.9591500860001</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>503.3630343891984</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$117,A2,'Species'!$U$2:$U$117))</x:f>
-        <x:v>876837.8435693181</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.698379941509302</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>499.3211263526533</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>869797.0048812523</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>7040.838688065764</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0080948067750901</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.008094806775090014</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>124.16691737789999</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>124.16691737789999</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$117,A3,'Species'!$U$2:$U$117))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>35810.1301363982</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>35810.1301363982</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>7356.420712241799</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.309983451107642</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2041.6601452520217</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>7356.420712241799</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2041.8342472215747</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$117,A4,'Species'!$U$2:$U$117))</x:f>
-        <x:v>15020591.747225435</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.309983451107642</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2041.6601452520217</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>15019310.979890574</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>1280.7673348616809</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.000085274706448</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.00008527470644801923</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>9742.614056421799</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.8740792973276137</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>748.3061203879791</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>9742.614056421799</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>760.169690934719</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$117,A5,'Species'!$U$2:$U$117))</x:f>
-        <x:v>7406039.916166408</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.8740792973276137</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>748.3061203879791</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>7290457.726998388</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>115582.18916802015</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0158539001933982</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.015853900193398066</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>859.9018853996</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.2712317547394525</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1867.3759221647842</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>859.9018853996</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1963.082552802065</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$117,A6,'Species'!$U$2:$U$117))</x:f>
-        <x:v>1688058.3883495557</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.2712317547394525</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1867.3759221647842</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1605760.0762193147</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>82298.31213024096</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0512519356714911</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.0512519356714911</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2.0810135018</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.719995658490446</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>524.8022139357873</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2.0810135018</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>524.8035127437336</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$117,A7,'Species'!$U$2:$U$117))</x:f>
-        <x:v>1092.123195811778</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.719995658490446</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>524.8022139357873</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1092.1204929749056</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0.002702836872458647</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.000002474852262</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0000024748522620395074</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>5581.7039900026</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.05</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1122.018454301963</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>5581.7039900026</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$117,A8,'Species'!$U$2:$U$117))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>6262774.883233816</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.05</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>6262774.883233816</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>3197.8977649062</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.174723070546064</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>149.52818801150082</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>3197.8977649062</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>153.27476216398483</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$117,A9,'Species'!$U$2:$U$117))</x:f>
-        <x:v>490157.01934073644</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.174723070546064</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>149.52818801150082</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>478175.8582324525</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>11981.161108283966</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0250559724043191</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.025055972404319175</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>164372.75830361352</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9167067914534908</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>825.4804484911468</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>164372.75830361352</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1148.1337826476301</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$117,A10,'Species'!$U$2:$U$117))</x:f>
-        <x:v>188721916.75535244</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9167067914534908</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>825.4804484911468</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>135686498.24419376</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>53035418.511158675</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.3908673242912593</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.39086732429125937</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>353132.63966014475</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.324066267911217</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>210.89499247894184</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>353132.63966014475</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>230.96424991287367</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$117,A11,'Species'!$U$2:$U$117))</x:f>
-        <x:v>81561015.23885843</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.324066267911217</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>210.89499247894184</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>74473905.3851951</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>7087109.853663325</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.095162323192362</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.095162323192362</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>347875.6435025259</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.2640131348957118</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>18.365938888489367</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>347875.6435025259</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>41.62765359307637</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$117,A12,'Species'!$U$2:$U$117))</x:f>
-        <x:v>14481246.781191677</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.2640131348957118</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>18.365938888489367</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>6389062.809361304</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>8092183.971830373</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>2.2665682296899075</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>1.2665682296899072</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>3383.7603114804</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>2.711422504578402</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>51.454398369465096</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>3383.7603114804</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>193.49218534687748</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$117,A13,'Species'!$U$2:$U$117))</x:f>
-        <x:v>654731.1773583734</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>2.711422504578402</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>51.454398369465096</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>174109.3510536978</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>480621.8263046756</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>3.760459581268814</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>2.760459581268814</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>28806.0635661192</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.248305832698519</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>17.713559183414493</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>28806.0635661192</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>17.908894769949697</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$117,A14,'Species'!$U$2:$U$117))</x:f>
-        <x:v>515884.7611421107</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.248305832698519</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>17.713559183414493</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>510257.91181965236</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>5626.849322458322</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0110274611958336</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.011027461195833643</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>92683.55686932801</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.7664803030590646</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>58.40907157103577</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>92683.55686932801</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>71.31106802925547</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$117,A15,'Species'!$U$2:$U$117))</x:f>
-        <x:v>6609363.429102018</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.7664803030590646</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>58.40907157103577</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>5413560.506638743</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1195802.9224632746</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2208902848683119</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.22089028486831186</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>6484.978737355</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.2425063006332433</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>174.78586197200013</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>6484.978737355</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>174.818412382361</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$117,A16,'Species'!$U$2:$U$117))</x:f>
-        <x:v>1133693.687197769</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.2425063006332433</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>174.78586197200013</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1133482.5984786868</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>211.08871908229776</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0001862302247653</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.00018623022476534908</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>3926.607957415</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.6137915478947846</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>410.9524253444099</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>3926.607957415</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>411.6048572811793</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$117,A17,'Species'!$U$2:$U$117))</x:f>
-        <x:v>1616210.907910944</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.6137915478947846</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>410.9524253444099</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>1613649.0634763537</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>2561.8444345903117</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0015876094081269</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0015876094081269567</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>77578.79527795811</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.4557464003289535</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>285.5922383844873</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>77578.79527795811</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>393.8235925533568</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$117,A18,'Species'!$U$2:$U$117))</x:f>
-        <x:v>30552359.862326853</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.4557464003289535</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>285.5922383844873</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>22155901.79460395</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>8396458.067722902</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.3789716232524487</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.37897162325244876</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>48.2374500802</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.4639844522388406</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>291.0612916133627</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>48.2374500802</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>300.11061780181245</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$117,A19,'Species'!$U$2:$U$117))</x:f>
-        <x:v>14476.570944752908</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.4639844522388406</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>291.0612916133627</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>14040.054524478117</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>436.516420274791</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.031090792383587</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.03109079238358704</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>7682.9327970996</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.5000486338457604</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>316.2631803133329</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>7682.9327970996</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>316.34462282851786</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$117,A20,'Species'!$U$2:$U$117))</x:f>
-        <x:v>2430454.477915323</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.5000486338457604</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>316.2631803133329</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>2429828.76054433</x:v>
       </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>625.7173709929921</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0002575150072932</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.000257515007293279</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd330f9667084fa9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3888b8ea78543cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10387,7 +9218,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10486,7 +9317,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>360072715.70051813</x:v>
+        <x:v>234022123.55637613</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10500,7 +9331,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>360072715.70051813</x:v>
+        <x:v>281557475.2599753</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10514,7 +9345,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-126050592.14414206</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10528,7 +9359,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-78515240.44054288</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10539,9 +9370,9 @@
         <x:v>EEZ_050</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10553,47 +9384,19 @@
         <x:v>EEZ_050</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_050</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_050</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c1a5706bbc04175"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R340050afae4f41cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10640,7 +9443,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
